--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,7 +599,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>75</v>
+      </c>
+      <c r="C5" t="n">
+        <v>45</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" t="n">
+        <v>158</v>
+      </c>
+      <c r="G5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H5" t="n">
+        <v>286</v>
+      </c>
+      <c r="I5" t="n">
+        <v>501</v>
+      </c>
+      <c r="J5" t="n">
+        <v>103</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,7 +638,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>75</v>
+      </c>
+      <c r="C6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16</v>
+      </c>
+      <c r="F6" t="n">
+        <v>157</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" t="n">
+        <v>280</v>
+      </c>
+      <c r="I6" t="n">
+        <v>568</v>
+      </c>
+      <c r="J6" t="n">
+        <v>48</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,7 +677,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>75</v>
+      </c>
+      <c r="C7" t="n">
+        <v>45</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>128</v>
+      </c>
+      <c r="G7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H7" t="n">
+        <v>270</v>
+      </c>
+      <c r="I7" t="n">
+        <v>603</v>
+      </c>
+      <c r="J7" t="n">
+        <v>35</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,7 +716,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>121</v>
+      </c>
+      <c r="C8" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="E8" t="n">
+        <v>68</v>
+      </c>
+      <c r="F8" t="n">
+        <v>139</v>
+      </c>
+      <c r="G8" t="n">
+        <v>72</v>
+      </c>
+      <c r="H8" t="n">
+        <v>297</v>
+      </c>
+      <c r="I8" t="n">
+        <v>624</v>
+      </c>
+      <c r="J8" t="n">
+        <v>147</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -724,38 +724,42 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>72.59999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="D8" t="n">
-        <v>7.26</v>
+        <v>0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>297</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>624</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>跳过(探测失败)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,6 +760,46 @@
           <t>The read operation timed out</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>75</v>
+      </c>
+      <c r="C9" t="n">
+        <v>45</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>14</v>
+      </c>
+      <c r="F9" t="n">
+        <v>73</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="n">
+        <v>299</v>
+      </c>
+      <c r="I9" t="n">
+        <v>719</v>
+      </c>
+      <c r="J9" t="n">
+        <v>40</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,7 +799,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>75</v>
+      </c>
+      <c r="C10" t="n">
+        <v>45</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>144</v>
+      </c>
+      <c r="G10" t="n">
+        <v>15</v>
+      </c>
+      <c r="H10" t="n">
+        <v>219</v>
+      </c>
+      <c r="I10" t="n">
+        <v>751</v>
+      </c>
+      <c r="J10" t="n">
+        <v>29</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C10" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="D10" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
@@ -835,10 +835,14 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>跳过(探测失败)</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -844,6 +844,46 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>75</v>
+      </c>
+      <c r="C11" t="n">
+        <v>45</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" t="n">
+        <v>152</v>
+      </c>
+      <c r="G11" t="n">
+        <v>32</v>
+      </c>
+      <c r="H11" t="n">
+        <v>244</v>
+      </c>
+      <c r="I11" t="n">
+        <v>770</v>
+      </c>
+      <c r="J11" t="n">
+        <v>44</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,7 +882,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>121</v>
+      </c>
+      <c r="C12" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="E12" t="n">
+        <v>43</v>
+      </c>
+      <c r="F12" t="n">
+        <v>105</v>
+      </c>
+      <c r="G12" t="n">
+        <v>196</v>
+      </c>
+      <c r="H12" t="n">
+        <v>199</v>
+      </c>
+      <c r="I12" t="n">
+        <v>803</v>
+      </c>
+      <c r="J12" t="n">
+        <v>270</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,46 +882,7 @@
           <t>正常</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>121</v>
-      </c>
-      <c r="C12" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="D12" t="n">
-        <v>7.26</v>
-      </c>
-      <c r="E12" t="n">
-        <v>43</v>
-      </c>
-      <c r="F12" t="n">
-        <v>105</v>
-      </c>
-      <c r="G12" t="n">
-        <v>196</v>
-      </c>
-      <c r="H12" t="n">
-        <v>199</v>
-      </c>
-      <c r="I12" t="n">
-        <v>803</v>
-      </c>
-      <c r="J12" t="n">
-        <v>270</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="12.08984375" customWidth="1" min="1" max="1"/>
@@ -1210,7 +1210,46 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>63</v>
+      </c>
+      <c r="C19" t="n">
+        <v>34</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>282</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>469</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1291</v>
+      </c>
+      <c r="J19" t="n">
+        <v>525</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -1218,31 +1218,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="C19" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="D19" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="F19" t="n">
-        <v>282</v>
+        <v>420</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="H19" t="n">
-        <v>469</v>
+        <v>675</v>
       </c>
       <c r="I19" t="n">
-        <v>1291</v>
+        <v>2582</v>
       </c>
       <c r="J19" t="n">
-        <v>525</v>
+        <v>1050</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
